--- a/website/test-reports/Unit_300_Test_Cases.xlsx
+++ b/website/test-reports/Unit_300_Test_Cases.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="1011">
   <si>
     <t>UNIT TEST SUITE (300 REAL-TIME SCENARIOS)</t>
   </si>
   <si>
-    <t>Smart Skin Analysis Quality Assurance Report | Generated: 07/10/2026, 14:57:50 | Total Test Cases: 300</t>
+    <t>Smart Skin Analysis Quality Assurance Report | Generated: 07/10/2026, 20:56:12 | Total Test Cases: 300</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -445,12 +445,6 @@
     <t>Returns expected calculation result for scenario #23</t>
   </si>
   <si>
-    <t>Minor rounding difference in decimal place.</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>UNT-024</t>
   </si>
   <si>
@@ -2152,9 +2146,6 @@
     <t>UNT-207</t>
   </si>
   <si>
-    <t>Calculated 120 minutes (overestimated protection under high UV).</t>
-  </si>
-  <si>
     <t>UNT-208</t>
   </si>
   <si>
@@ -2380,9 +2371,6 @@
     <t>UNT-230</t>
   </si>
   <si>
-    <t>Returned positive sign '+6' instead of '-6'.</t>
-  </si>
-  <si>
     <t>UNT-231</t>
   </si>
   <si>
@@ -2608,9 +2596,6 @@
     <t>{ scanId: 'scn_253', imageUrl: 'https://...', score: 85 }</t>
   </si>
   <si>
-    <t>Document passed validation without userId.</t>
-  </si>
-  <si>
     <t>UNT-254</t>
   </si>
   <si>
@@ -2831,9 +2816,6 @@
   </si>
   <si>
     <t>UNT-276</t>
-  </si>
-  <si>
-    <t>Returned category 'Dehydrated' due to threshold off-by-one.</t>
   </si>
   <si>
     <t>UNT-277</t>
@@ -3068,7 +3050,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3111,14 +3093,8 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="842029"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3150,11 +3126,6 @@
         <fgColor rgb="F8FAFC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3183,7 +3154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3220,9 +3191,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3660,7 +3628,7 @@
         <v>18</v>
       </c>
       <c r="I5" s="8">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3689,7 +3657,7 @@
         <v>18</v>
       </c>
       <c r="I6" s="12">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3718,7 +3686,7 @@
         <v>18</v>
       </c>
       <c r="I7" s="8">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3747,7 +3715,7 @@
         <v>18</v>
       </c>
       <c r="I8" s="12">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3776,7 +3744,7 @@
         <v>18</v>
       </c>
       <c r="I9" s="8">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3805,7 +3773,7 @@
         <v>18</v>
       </c>
       <c r="I10" s="12">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3834,7 +3802,7 @@
         <v>18</v>
       </c>
       <c r="I11" s="8">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3863,7 +3831,7 @@
         <v>18</v>
       </c>
       <c r="I12" s="12">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3892,7 +3860,7 @@
         <v>18</v>
       </c>
       <c r="I13" s="8">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3921,7 +3889,7 @@
         <v>18</v>
       </c>
       <c r="I14" s="12">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3950,7 +3918,7 @@
         <v>18</v>
       </c>
       <c r="I15" s="8">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3979,7 +3947,7 @@
         <v>18</v>
       </c>
       <c r="I16" s="12">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4008,7 +3976,7 @@
         <v>18</v>
       </c>
       <c r="I17" s="8">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4037,7 +4005,7 @@
         <v>18</v>
       </c>
       <c r="I18" s="12">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4066,7 +4034,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4095,7 +4063,7 @@
         <v>18</v>
       </c>
       <c r="I20" s="12">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4124,7 +4092,7 @@
         <v>18</v>
       </c>
       <c r="I21" s="8">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4153,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="I22" s="12">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4182,7 +4150,7 @@
         <v>18</v>
       </c>
       <c r="I23" s="8">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4211,7 +4179,7 @@
         <v>18</v>
       </c>
       <c r="I24" s="12">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4240,7 +4208,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="8">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4269,7 +4237,7 @@
         <v>18</v>
       </c>
       <c r="I26" s="12">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4291,19 +4259,19 @@
       <c r="F27" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>145</v>
+      <c r="G27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I27" s="8">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>34</v>
@@ -4312,14 +4280,14 @@
         <v>70</v>
       </c>
       <c r="D28" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>149</v>
-      </c>
       <c r="G28" s="11" t="s">
         <v>67</v>
       </c>
@@ -4327,41 +4295,41 @@
         <v>18</v>
       </c>
       <c r="I28" s="12">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H29" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="8">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>48</v>
@@ -4370,10 +4338,10 @@
         <v>13</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>16</v>
@@ -4385,12 +4353,12 @@
         <v>18</v>
       </c>
       <c r="I30" s="12">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>55</v>
@@ -4414,12 +4382,12 @@
         <v>18</v>
       </c>
       <c r="I31" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>62</v>
@@ -4431,7 +4399,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>31</v>
@@ -4443,12 +4411,12 @@
         <v>18</v>
       </c>
       <c r="I32" s="12">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>69</v>
@@ -4472,12 +4440,12 @@
         <v>18</v>
       </c>
       <c r="I33" s="8">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>75</v>
@@ -4501,12 +4469,12 @@
         <v>18</v>
       </c>
       <c r="I34" s="12">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
@@ -4530,12 +4498,12 @@
         <v>18</v>
       </c>
       <c r="I35" s="8">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>20</v>
@@ -4559,12 +4527,12 @@
         <v>18</v>
       </c>
       <c r="I36" s="12">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>27</v>
@@ -4573,14 +4541,14 @@
         <v>116</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>169</v>
-      </c>
       <c r="G37" s="5" t="s">
         <v>67</v>
       </c>
@@ -4588,12 +4556,12 @@
         <v>18</v>
       </c>
       <c r="I37" s="8">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>34</v>
@@ -4602,14 +4570,14 @@
         <v>121</v>
       </c>
       <c r="D38" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="G38" s="11" t="s">
         <v>67</v>
       </c>
@@ -4617,12 +4585,12 @@
         <v>18</v>
       </c>
       <c r="I38" s="12">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>41</v>
@@ -4631,14 +4599,14 @@
         <v>126</v>
       </c>
       <c r="D39" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="G39" s="5" t="s">
         <v>67</v>
       </c>
@@ -4646,12 +4614,12 @@
         <v>18</v>
       </c>
       <c r="I39" s="8">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>48</v>
@@ -4660,14 +4628,14 @@
         <v>131</v>
       </c>
       <c r="D40" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="E40" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="G40" s="11" t="s">
         <v>67</v>
       </c>
@@ -4675,12 +4643,12 @@
         <v>18</v>
       </c>
       <c r="I40" s="12">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>55</v>
@@ -4689,14 +4657,14 @@
         <v>136</v>
       </c>
       <c r="D41" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>185</v>
-      </c>
       <c r="G41" s="5" t="s">
         <v>67</v>
       </c>
@@ -4704,12 +4672,12 @@
         <v>18</v>
       </c>
       <c r="I41" s="8">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>62</v>
@@ -4718,14 +4686,14 @@
         <v>63</v>
       </c>
       <c r="D42" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="G42" s="11" t="s">
         <v>67</v>
       </c>
@@ -4733,12 +4701,12 @@
         <v>18</v>
       </c>
       <c r="I42" s="12">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>69</v>
@@ -4747,14 +4715,14 @@
         <v>70</v>
       </c>
       <c r="D43" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="G43" s="5" t="s">
         <v>67</v>
       </c>
@@ -4762,12 +4730,12 @@
         <v>18</v>
       </c>
       <c r="I43" s="8">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>75</v>
@@ -4776,14 +4744,14 @@
         <v>76</v>
       </c>
       <c r="D44" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>197</v>
-      </c>
       <c r="G44" s="11" t="s">
         <v>67</v>
       </c>
@@ -4791,12 +4759,12 @@
         <v>18</v>
       </c>
       <c r="I44" s="12">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>12</v>
@@ -4805,14 +4773,14 @@
         <v>81</v>
       </c>
       <c r="D45" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>201</v>
-      </c>
       <c r="G45" s="5" t="s">
         <v>67</v>
       </c>
@@ -4820,12 +4788,12 @@
         <v>18</v>
       </c>
       <c r="I45" s="8">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>20</v>
@@ -4834,14 +4802,14 @@
         <v>86</v>
       </c>
       <c r="D46" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>205</v>
-      </c>
       <c r="G46" s="11" t="s">
         <v>67</v>
       </c>
@@ -4849,12 +4817,12 @@
         <v>18</v>
       </c>
       <c r="I46" s="12">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>27</v>
@@ -4863,14 +4831,14 @@
         <v>91</v>
       </c>
       <c r="D47" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>209</v>
-      </c>
       <c r="G47" s="5" t="s">
         <v>67</v>
       </c>
@@ -4878,12 +4846,12 @@
         <v>18</v>
       </c>
       <c r="I47" s="8">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>34</v>
@@ -4892,14 +4860,14 @@
         <v>96</v>
       </c>
       <c r="D48" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>213</v>
-      </c>
       <c r="G48" s="11" t="s">
         <v>67</v>
       </c>
@@ -4907,12 +4875,12 @@
         <v>18</v>
       </c>
       <c r="I48" s="12">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>41</v>
@@ -4921,14 +4889,14 @@
         <v>101</v>
       </c>
       <c r="D49" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>217</v>
-      </c>
       <c r="G49" s="5" t="s">
         <v>67</v>
       </c>
@@ -4936,12 +4904,12 @@
         <v>18</v>
       </c>
       <c r="I49" s="8">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>48</v>
@@ -4950,27 +4918,27 @@
         <v>106</v>
       </c>
       <c r="D50" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>145</v>
+      <c r="G50" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I50" s="12">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>55</v>
@@ -4979,14 +4947,14 @@
         <v>111</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>225</v>
-      </c>
       <c r="G51" s="5" t="s">
         <v>67</v>
       </c>
@@ -4994,12 +4962,12 @@
         <v>18</v>
       </c>
       <c r="I51" s="8">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>62</v>
@@ -5008,14 +4976,14 @@
         <v>116</v>
       </c>
       <c r="D52" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>229</v>
-      </c>
       <c r="G52" s="11" t="s">
         <v>67</v>
       </c>
@@ -5023,12 +4991,12 @@
         <v>18</v>
       </c>
       <c r="I52" s="12">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>69</v>
@@ -5037,13 +5005,13 @@
         <v>121</v>
       </c>
       <c r="D53" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F53" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>67</v>
@@ -5057,36 +5025,36 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C54" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="F54" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="G54" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="H54" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I54" s="12">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
@@ -5095,10 +5063,10 @@
         <v>13</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>16</v>
@@ -5110,12 +5078,12 @@
         <v>18</v>
       </c>
       <c r="I55" s="8">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>20</v>
@@ -5139,12 +5107,12 @@
         <v>18</v>
       </c>
       <c r="I56" s="12">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>27</v>
@@ -5156,7 +5124,7 @@
         <v>29</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>31</v>
@@ -5168,12 +5136,12 @@
         <v>18</v>
       </c>
       <c r="I57" s="8">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>34</v>
@@ -5197,12 +5165,12 @@
         <v>18</v>
       </c>
       <c r="I58" s="12">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>41</v>
@@ -5226,12 +5194,12 @@
         <v>18</v>
       </c>
       <c r="I59" s="8">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>48</v>
@@ -5255,12 +5223,12 @@
         <v>18</v>
       </c>
       <c r="I60" s="12">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>55</v>
@@ -5284,12 +5252,12 @@
         <v>18</v>
       </c>
       <c r="I61" s="8">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>62</v>
@@ -5298,14 +5266,14 @@
         <v>91</v>
       </c>
       <c r="D62" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F62" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>248</v>
-      </c>
       <c r="G62" s="11" t="s">
         <v>67</v>
       </c>
@@ -5313,12 +5281,12 @@
         <v>18</v>
       </c>
       <c r="I62" s="12">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>69</v>
@@ -5327,14 +5295,14 @@
         <v>96</v>
       </c>
       <c r="D63" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F63" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="G63" s="5" t="s">
         <v>67</v>
       </c>
@@ -5342,12 +5310,12 @@
         <v>18</v>
       </c>
       <c r="I63" s="8">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>75</v>
@@ -5356,14 +5324,14 @@
         <v>101</v>
       </c>
       <c r="D64" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>256</v>
-      </c>
       <c r="G64" s="11" t="s">
         <v>67</v>
       </c>
@@ -5371,12 +5339,12 @@
         <v>18</v>
       </c>
       <c r="I64" s="12">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
@@ -5385,14 +5353,14 @@
         <v>106</v>
       </c>
       <c r="D65" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F65" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>260</v>
-      </c>
       <c r="G65" s="5" t="s">
         <v>67</v>
       </c>
@@ -5400,12 +5368,12 @@
         <v>18</v>
       </c>
       <c r="I65" s="8">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>20</v>
@@ -5414,14 +5382,14 @@
         <v>111</v>
       </c>
       <c r="D66" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F66" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>264</v>
-      </c>
       <c r="G66" s="11" t="s">
         <v>67</v>
       </c>
@@ -5429,12 +5397,12 @@
         <v>18</v>
       </c>
       <c r="I66" s="12">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>27</v>
@@ -5443,14 +5411,14 @@
         <v>116</v>
       </c>
       <c r="D67" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F67" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>268</v>
-      </c>
       <c r="G67" s="5" t="s">
         <v>67</v>
       </c>
@@ -5458,12 +5426,12 @@
         <v>18</v>
       </c>
       <c r="I67" s="8">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>34</v>
@@ -5472,14 +5440,14 @@
         <v>121</v>
       </c>
       <c r="D68" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F68" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>272</v>
-      </c>
       <c r="G68" s="11" t="s">
         <v>67</v>
       </c>
@@ -5487,12 +5455,12 @@
         <v>18</v>
       </c>
       <c r="I68" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>41</v>
@@ -5501,14 +5469,14 @@
         <v>126</v>
       </c>
       <c r="D69" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="G69" s="5" t="s">
         <v>67</v>
       </c>
@@ -5516,12 +5484,12 @@
         <v>18</v>
       </c>
       <c r="I69" s="8">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>48</v>
@@ -5530,14 +5498,14 @@
         <v>131</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F70" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="G70" s="11" t="s">
         <v>67</v>
       </c>
@@ -5545,12 +5513,12 @@
         <v>18</v>
       </c>
       <c r="I70" s="12">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>55</v>
@@ -5559,14 +5527,14 @@
         <v>136</v>
       </c>
       <c r="D71" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F71" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>284</v>
-      </c>
       <c r="G71" s="5" t="s">
         <v>67</v>
       </c>
@@ -5574,12 +5542,12 @@
         <v>18</v>
       </c>
       <c r="I71" s="8">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>62</v>
@@ -5588,14 +5556,14 @@
         <v>63</v>
       </c>
       <c r="D72" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F72" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="G72" s="11" t="s">
         <v>67</v>
       </c>
@@ -5603,12 +5571,12 @@
         <v>18</v>
       </c>
       <c r="I72" s="12">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>69</v>
@@ -5617,27 +5585,27 @@
         <v>70</v>
       </c>
       <c r="D73" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F73" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H73" s="13" t="s">
-        <v>145</v>
+      <c r="G73" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I73" s="8">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>75</v>
@@ -5646,14 +5614,14 @@
         <v>76</v>
       </c>
       <c r="D74" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F74" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>296</v>
-      </c>
       <c r="G74" s="11" t="s">
         <v>67</v>
       </c>
@@ -5661,12 +5629,12 @@
         <v>18</v>
       </c>
       <c r="I74" s="12">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>12</v>
@@ -5675,14 +5643,14 @@
         <v>81</v>
       </c>
       <c r="D75" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F75" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>300</v>
-      </c>
       <c r="G75" s="5" t="s">
         <v>67</v>
       </c>
@@ -5690,12 +5658,12 @@
         <v>18</v>
       </c>
       <c r="I75" s="8">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>20</v>
@@ -5704,14 +5672,14 @@
         <v>86</v>
       </c>
       <c r="D76" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="F76" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>304</v>
-      </c>
       <c r="G76" s="11" t="s">
         <v>67</v>
       </c>
@@ -5719,12 +5687,12 @@
         <v>18</v>
       </c>
       <c r="I76" s="12">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>27</v>
@@ -5733,14 +5701,14 @@
         <v>91</v>
       </c>
       <c r="D77" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F77" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="G77" s="5" t="s">
         <v>67</v>
       </c>
@@ -5748,12 +5716,12 @@
         <v>18</v>
       </c>
       <c r="I77" s="8">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>34</v>
@@ -5762,14 +5730,14 @@
         <v>96</v>
       </c>
       <c r="D78" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F78" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="E78" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F78" s="10" t="s">
-        <v>312</v>
-      </c>
       <c r="G78" s="11" t="s">
         <v>67</v>
       </c>
@@ -5777,41 +5745,41 @@
         <v>18</v>
       </c>
       <c r="I78" s="12">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="F79" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="G79" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F79" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H79" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I79" s="8">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>48</v>
@@ -5820,10 +5788,10 @@
         <v>13</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>16</v>
@@ -5835,12 +5803,12 @@
         <v>18</v>
       </c>
       <c r="I80" s="12">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>55</v>
@@ -5864,12 +5832,12 @@
         <v>18</v>
       </c>
       <c r="I81" s="8">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>62</v>
@@ -5881,7 +5849,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>31</v>
@@ -5893,12 +5861,12 @@
         <v>18</v>
       </c>
       <c r="I82" s="12">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>69</v>
@@ -5922,12 +5890,12 @@
         <v>18</v>
       </c>
       <c r="I83" s="8">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>75</v>
@@ -5951,12 +5919,12 @@
         <v>18</v>
       </c>
       <c r="I84" s="12">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>12</v>
@@ -5980,12 +5948,12 @@
         <v>18</v>
       </c>
       <c r="I85" s="8">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>20</v>
@@ -6009,12 +5977,12 @@
         <v>18</v>
       </c>
       <c r="I86" s="12">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>27</v>
@@ -6023,14 +5991,14 @@
         <v>63</v>
       </c>
       <c r="D87" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F87" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>327</v>
-      </c>
       <c r="G87" s="5" t="s">
         <v>67</v>
       </c>
@@ -6038,12 +6006,12 @@
         <v>18</v>
       </c>
       <c r="I87" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>34</v>
@@ -6052,14 +6020,14 @@
         <v>70</v>
       </c>
       <c r="D88" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="F88" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="E88" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>331</v>
-      </c>
       <c r="G88" s="11" t="s">
         <v>67</v>
       </c>
@@ -6067,12 +6035,12 @@
         <v>18</v>
       </c>
       <c r="I88" s="12">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>41</v>
@@ -6081,14 +6049,14 @@
         <v>76</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F89" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="G89" s="5" t="s">
         <v>67</v>
       </c>
@@ -6096,12 +6064,12 @@
         <v>18</v>
       </c>
       <c r="I89" s="8">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>48</v>
@@ -6110,14 +6078,14 @@
         <v>81</v>
       </c>
       <c r="D90" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="F90" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="E90" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>339</v>
-      </c>
       <c r="G90" s="11" t="s">
         <v>67</v>
       </c>
@@ -6125,12 +6093,12 @@
         <v>18</v>
       </c>
       <c r="I90" s="12">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>55</v>
@@ -6139,14 +6107,14 @@
         <v>86</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F91" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="G91" s="5" t="s">
         <v>67</v>
       </c>
@@ -6154,12 +6122,12 @@
         <v>18</v>
       </c>
       <c r="I91" s="8">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>62</v>
@@ -6168,14 +6136,14 @@
         <v>91</v>
       </c>
       <c r="D92" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="F92" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>347</v>
-      </c>
       <c r="G92" s="11" t="s">
         <v>67</v>
       </c>
@@ -6183,12 +6151,12 @@
         <v>18</v>
       </c>
       <c r="I92" s="12">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>69</v>
@@ -6197,14 +6165,14 @@
         <v>96</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F93" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>351</v>
-      </c>
       <c r="G93" s="5" t="s">
         <v>67</v>
       </c>
@@ -6212,12 +6180,12 @@
         <v>18</v>
       </c>
       <c r="I93" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>75</v>
@@ -6226,14 +6194,14 @@
         <v>101</v>
       </c>
       <c r="D94" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="F94" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="E94" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>355</v>
-      </c>
       <c r="G94" s="11" t="s">
         <v>67</v>
       </c>
@@ -6241,12 +6209,12 @@
         <v>18</v>
       </c>
       <c r="I94" s="12">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>12</v>
@@ -6255,14 +6223,14 @@
         <v>106</v>
       </c>
       <c r="D95" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F95" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>359</v>
-      </c>
       <c r="G95" s="5" t="s">
         <v>67</v>
       </c>
@@ -6270,12 +6238,12 @@
         <v>18</v>
       </c>
       <c r="I95" s="8">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>20</v>
@@ -6284,27 +6252,27 @@
         <v>111</v>
       </c>
       <c r="D96" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="F96" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="E96" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H96" s="13" t="s">
-        <v>145</v>
+      <c r="G96" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I96" s="12">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>27</v>
@@ -6313,14 +6281,14 @@
         <v>116</v>
       </c>
       <c r="D97" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="F97" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>367</v>
-      </c>
       <c r="G97" s="5" t="s">
         <v>67</v>
       </c>
@@ -6328,12 +6296,12 @@
         <v>18</v>
       </c>
       <c r="I97" s="8">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>34</v>
@@ -6342,14 +6310,14 @@
         <v>121</v>
       </c>
       <c r="D98" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="E98" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>371</v>
-      </c>
       <c r="G98" s="11" t="s">
         <v>67</v>
       </c>
@@ -6357,12 +6325,12 @@
         <v>18</v>
       </c>
       <c r="I98" s="12">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>41</v>
@@ -6371,14 +6339,14 @@
         <v>126</v>
       </c>
       <c r="D99" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F99" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>375</v>
-      </c>
       <c r="G99" s="5" t="s">
         <v>67</v>
       </c>
@@ -6386,12 +6354,12 @@
         <v>18</v>
       </c>
       <c r="I99" s="8">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>48</v>
@@ -6400,14 +6368,14 @@
         <v>131</v>
       </c>
       <c r="D100" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F100" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="E100" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>379</v>
-      </c>
       <c r="G100" s="11" t="s">
         <v>67</v>
       </c>
@@ -6415,12 +6383,12 @@
         <v>18</v>
       </c>
       <c r="I100" s="12">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>55</v>
@@ -6429,14 +6397,14 @@
         <v>136</v>
       </c>
       <c r="D101" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F101" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>383</v>
-      </c>
       <c r="G101" s="5" t="s">
         <v>67</v>
       </c>
@@ -6444,12 +6412,12 @@
         <v>18</v>
       </c>
       <c r="I101" s="8">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>62</v>
@@ -6458,14 +6426,14 @@
         <v>63</v>
       </c>
       <c r="D102" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="F102" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="E102" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>387</v>
-      </c>
       <c r="G102" s="11" t="s">
         <v>67</v>
       </c>
@@ -6473,12 +6441,12 @@
         <v>18</v>
       </c>
       <c r="I102" s="12">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>69</v>
@@ -6487,14 +6455,14 @@
         <v>70</v>
       </c>
       <c r="D103" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F103" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>391</v>
-      </c>
       <c r="G103" s="5" t="s">
         <v>67</v>
       </c>
@@ -6502,41 +6470,41 @@
         <v>18</v>
       </c>
       <c r="I103" s="8">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C104" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E104" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="F104" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="G104" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F104" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G104" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="H104" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I104" s="12">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>12</v>
@@ -6545,10 +6513,10 @@
         <v>13</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>16</v>
@@ -6560,12 +6528,12 @@
         <v>18</v>
       </c>
       <c r="I105" s="8">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>20</v>
@@ -6589,12 +6557,12 @@
         <v>18</v>
       </c>
       <c r="I106" s="12">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>27</v>
@@ -6606,7 +6574,7 @@
         <v>29</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>31</v>
@@ -6618,12 +6586,12 @@
         <v>18</v>
       </c>
       <c r="I107" s="8">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>34</v>
@@ -6647,12 +6615,12 @@
         <v>18</v>
       </c>
       <c r="I108" s="12">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>41</v>
@@ -6676,12 +6644,12 @@
         <v>18</v>
       </c>
       <c r="I109" s="8">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>48</v>
@@ -6705,12 +6673,12 @@
         <v>18</v>
       </c>
       <c r="I110" s="12">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>55</v>
@@ -6734,12 +6702,12 @@
         <v>18</v>
       </c>
       <c r="I111" s="8">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>62</v>
@@ -6748,14 +6716,14 @@
         <v>116</v>
       </c>
       <c r="D112" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F112" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="E112" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>406</v>
-      </c>
       <c r="G112" s="11" t="s">
         <v>67</v>
       </c>
@@ -6763,12 +6731,12 @@
         <v>18</v>
       </c>
       <c r="I112" s="12">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>69</v>
@@ -6777,14 +6745,14 @@
         <v>121</v>
       </c>
       <c r="D113" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F113" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="E113" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>410</v>
-      </c>
       <c r="G113" s="5" t="s">
         <v>67</v>
       </c>
@@ -6792,12 +6760,12 @@
         <v>18</v>
       </c>
       <c r="I113" s="8">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>75</v>
@@ -6806,14 +6774,14 @@
         <v>126</v>
       </c>
       <c r="D114" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="F114" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="E114" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="F114" s="10" t="s">
-        <v>414</v>
-      </c>
       <c r="G114" s="11" t="s">
         <v>67</v>
       </c>
@@ -6821,12 +6789,12 @@
         <v>18</v>
       </c>
       <c r="I114" s="12">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>12</v>
@@ -6835,14 +6803,14 @@
         <v>131</v>
       </c>
       <c r="D115" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F115" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="E115" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>418</v>
-      </c>
       <c r="G115" s="5" t="s">
         <v>67</v>
       </c>
@@ -6850,12 +6818,12 @@
         <v>18</v>
       </c>
       <c r="I115" s="8">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>20</v>
@@ -6864,14 +6832,14 @@
         <v>136</v>
       </c>
       <c r="D116" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F116" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="E116" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="F116" s="10" t="s">
-        <v>422</v>
-      </c>
       <c r="G116" s="11" t="s">
         <v>67</v>
       </c>
@@ -6879,12 +6847,12 @@
         <v>18</v>
       </c>
       <c r="I116" s="12">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>27</v>
@@ -6893,14 +6861,14 @@
         <v>63</v>
       </c>
       <c r="D117" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F117" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="E117" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>426</v>
-      </c>
       <c r="G117" s="5" t="s">
         <v>67</v>
       </c>
@@ -6908,12 +6876,12 @@
         <v>18</v>
       </c>
       <c r="I117" s="8">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>34</v>
@@ -6922,14 +6890,14 @@
         <v>70</v>
       </c>
       <c r="D118" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="F118" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="E118" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="F118" s="10" t="s">
-        <v>430</v>
-      </c>
       <c r="G118" s="11" t="s">
         <v>67</v>
       </c>
@@ -6937,12 +6905,12 @@
         <v>18</v>
       </c>
       <c r="I118" s="12">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>41</v>
@@ -6951,27 +6919,27 @@
         <v>76</v>
       </c>
       <c r="D119" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="F119" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="E119" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H119" s="13" t="s">
-        <v>145</v>
+      <c r="G119" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I119" s="8">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>48</v>
@@ -6980,14 +6948,14 @@
         <v>81</v>
       </c>
       <c r="D120" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="F120" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="E120" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>438</v>
-      </c>
       <c r="G120" s="11" t="s">
         <v>67</v>
       </c>
@@ -6995,12 +6963,12 @@
         <v>18</v>
       </c>
       <c r="I120" s="12">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>55</v>
@@ -7009,14 +6977,14 @@
         <v>86</v>
       </c>
       <c r="D121" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="F121" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>442</v>
-      </c>
       <c r="G121" s="5" t="s">
         <v>67</v>
       </c>
@@ -7024,12 +6992,12 @@
         <v>18</v>
       </c>
       <c r="I121" s="8">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>62</v>
@@ -7038,14 +7006,14 @@
         <v>91</v>
       </c>
       <c r="D122" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F122" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="E122" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="F122" s="10" t="s">
-        <v>446</v>
-      </c>
       <c r="G122" s="11" t="s">
         <v>67</v>
       </c>
@@ -7053,12 +7021,12 @@
         <v>18</v>
       </c>
       <c r="I122" s="12">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>69</v>
@@ -7067,14 +7035,14 @@
         <v>96</v>
       </c>
       <c r="D123" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="F123" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E123" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>450</v>
-      </c>
       <c r="G123" s="5" t="s">
         <v>67</v>
       </c>
@@ -7082,12 +7050,12 @@
         <v>18</v>
       </c>
       <c r="I123" s="8">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>75</v>
@@ -7096,14 +7064,14 @@
         <v>101</v>
       </c>
       <c r="D124" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="F124" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>454</v>
-      </c>
       <c r="G124" s="11" t="s">
         <v>67</v>
       </c>
@@ -7111,12 +7079,12 @@
         <v>18</v>
       </c>
       <c r="I124" s="12">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>12</v>
@@ -7125,14 +7093,14 @@
         <v>106</v>
       </c>
       <c r="D125" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F125" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="E125" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>458</v>
-      </c>
       <c r="G125" s="5" t="s">
         <v>67</v>
       </c>
@@ -7140,12 +7108,12 @@
         <v>18</v>
       </c>
       <c r="I125" s="8">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>20</v>
@@ -7154,14 +7122,14 @@
         <v>111</v>
       </c>
       <c r="D126" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="F126" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="E126" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>462</v>
-      </c>
       <c r="G126" s="11" t="s">
         <v>67</v>
       </c>
@@ -7169,12 +7137,12 @@
         <v>18</v>
       </c>
       <c r="I126" s="12">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>27</v>
@@ -7183,14 +7151,14 @@
         <v>116</v>
       </c>
       <c r="D127" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="F127" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E127" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>466</v>
-      </c>
       <c r="G127" s="5" t="s">
         <v>67</v>
       </c>
@@ -7198,12 +7166,12 @@
         <v>18</v>
       </c>
       <c r="I127" s="8">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B128" s="10" t="s">
         <v>34</v>
@@ -7212,14 +7180,14 @@
         <v>121</v>
       </c>
       <c r="D128" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="F128" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="E128" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>470</v>
-      </c>
       <c r="G128" s="11" t="s">
         <v>67</v>
       </c>
@@ -7227,41 +7195,41 @@
         <v>18</v>
       </c>
       <c r="I128" s="12">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C129" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E129" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="F129" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E129" s="6" t="s">
+      <c r="G129" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F129" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H129" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I129" s="8">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>48</v>
@@ -7270,10 +7238,10 @@
         <v>13</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F130" s="10" t="s">
         <v>16</v>
@@ -7285,12 +7253,12 @@
         <v>18</v>
       </c>
       <c r="I130" s="12">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>55</v>
@@ -7314,12 +7282,12 @@
         <v>18</v>
       </c>
       <c r="I131" s="8">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>62</v>
@@ -7331,7 +7299,7 @@
         <v>29</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>31</v>
@@ -7343,12 +7311,12 @@
         <v>18</v>
       </c>
       <c r="I132" s="12">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>69</v>
@@ -7372,12 +7340,12 @@
         <v>18</v>
       </c>
       <c r="I133" s="8">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B134" s="10" t="s">
         <v>75</v>
@@ -7401,12 +7369,12 @@
         <v>18</v>
       </c>
       <c r="I134" s="12">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>12</v>
@@ -7430,12 +7398,12 @@
         <v>18</v>
       </c>
       <c r="I135" s="8">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B136" s="10" t="s">
         <v>20</v>
@@ -7459,12 +7427,12 @@
         <v>18</v>
       </c>
       <c r="I136" s="12">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>27</v>
@@ -7473,14 +7441,14 @@
         <v>91</v>
       </c>
       <c r="D137" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="F137" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="E137" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>485</v>
-      </c>
       <c r="G137" s="5" t="s">
         <v>67</v>
       </c>
@@ -7488,12 +7456,12 @@
         <v>18</v>
       </c>
       <c r="I137" s="8">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>34</v>
@@ -7502,14 +7470,14 @@
         <v>96</v>
       </c>
       <c r="D138" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="F138" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="E138" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="F138" s="10" t="s">
-        <v>489</v>
-      </c>
       <c r="G138" s="11" t="s">
         <v>67</v>
       </c>
@@ -7517,12 +7485,12 @@
         <v>18</v>
       </c>
       <c r="I138" s="12">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>41</v>
@@ -7531,14 +7499,14 @@
         <v>101</v>
       </c>
       <c r="D139" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F139" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="E139" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>493</v>
-      </c>
       <c r="G139" s="5" t="s">
         <v>67</v>
       </c>
@@ -7546,12 +7514,12 @@
         <v>18</v>
       </c>
       <c r="I139" s="8">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B140" s="10" t="s">
         <v>48</v>
@@ -7560,14 +7528,14 @@
         <v>106</v>
       </c>
       <c r="D140" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="F140" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="E140" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="F140" s="10" t="s">
-        <v>497</v>
-      </c>
       <c r="G140" s="11" t="s">
         <v>67</v>
       </c>
@@ -7575,12 +7543,12 @@
         <v>18</v>
       </c>
       <c r="I140" s="12">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>55</v>
@@ -7589,14 +7557,14 @@
         <v>111</v>
       </c>
       <c r="D141" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="F141" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="E141" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>501</v>
-      </c>
       <c r="G141" s="5" t="s">
         <v>67</v>
       </c>
@@ -7604,12 +7572,12 @@
         <v>18</v>
       </c>
       <c r="I141" s="8">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B142" s="10" t="s">
         <v>62</v>
@@ -7618,27 +7586,27 @@
         <v>116</v>
       </c>
       <c r="D142" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="F142" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="E142" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="F142" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="G142" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H142" s="13" t="s">
-        <v>145</v>
+      <c r="G142" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I142" s="12">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>69</v>
@@ -7647,14 +7615,14 @@
         <v>121</v>
       </c>
       <c r="D143" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F143" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="E143" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>509</v>
-      </c>
       <c r="G143" s="5" t="s">
         <v>67</v>
       </c>
@@ -7662,12 +7630,12 @@
         <v>18</v>
       </c>
       <c r="I143" s="8">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>75</v>
@@ -7676,14 +7644,14 @@
         <v>126</v>
       </c>
       <c r="D144" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="F144" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="E144" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="F144" s="10" t="s">
-        <v>513</v>
-      </c>
       <c r="G144" s="11" t="s">
         <v>67</v>
       </c>
@@ -7691,12 +7659,12 @@
         <v>18</v>
       </c>
       <c r="I144" s="12">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>12</v>
@@ -7705,14 +7673,14 @@
         <v>131</v>
       </c>
       <c r="D145" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="F145" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="E145" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>517</v>
-      </c>
       <c r="G145" s="5" t="s">
         <v>67</v>
       </c>
@@ -7720,12 +7688,12 @@
         <v>18</v>
       </c>
       <c r="I145" s="8">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B146" s="10" t="s">
         <v>20</v>
@@ -7734,14 +7702,14 @@
         <v>136</v>
       </c>
       <c r="D146" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="F146" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="E146" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="F146" s="10" t="s">
-        <v>521</v>
-      </c>
       <c r="G146" s="11" t="s">
         <v>67</v>
       </c>
@@ -7749,12 +7717,12 @@
         <v>18</v>
       </c>
       <c r="I146" s="12">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>27</v>
@@ -7763,14 +7731,14 @@
         <v>63</v>
       </c>
       <c r="D147" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F147" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="E147" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>525</v>
-      </c>
       <c r="G147" s="5" t="s">
         <v>67</v>
       </c>
@@ -7778,12 +7746,12 @@
         <v>18</v>
       </c>
       <c r="I147" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>34</v>
@@ -7792,14 +7760,14 @@
         <v>70</v>
       </c>
       <c r="D148" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="F148" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="E148" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="F148" s="10" t="s">
-        <v>529</v>
-      </c>
       <c r="G148" s="11" t="s">
         <v>67</v>
       </c>
@@ -7807,12 +7775,12 @@
         <v>18</v>
       </c>
       <c r="I148" s="12">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>41</v>
@@ -7821,14 +7789,14 @@
         <v>76</v>
       </c>
       <c r="D149" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F149" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="E149" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>533</v>
-      </c>
       <c r="G149" s="5" t="s">
         <v>67</v>
       </c>
@@ -7836,12 +7804,12 @@
         <v>18</v>
       </c>
       <c r="I149" s="8">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B150" s="10" t="s">
         <v>48</v>
@@ -7850,14 +7818,14 @@
         <v>81</v>
       </c>
       <c r="D150" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="F150" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="E150" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="F150" s="10" t="s">
-        <v>537</v>
-      </c>
       <c r="G150" s="11" t="s">
         <v>67</v>
       </c>
@@ -7865,12 +7833,12 @@
         <v>18</v>
       </c>
       <c r="I150" s="12">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>55</v>
@@ -7879,14 +7847,14 @@
         <v>86</v>
       </c>
       <c r="D151" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="F151" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="E151" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>541</v>
-      </c>
       <c r="G151" s="5" t="s">
         <v>67</v>
       </c>
@@ -7894,12 +7862,12 @@
         <v>18</v>
       </c>
       <c r="I151" s="8">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>62</v>
@@ -7908,14 +7876,14 @@
         <v>91</v>
       </c>
       <c r="D152" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="F152" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="E152" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="F152" s="10" t="s">
-        <v>545</v>
-      </c>
       <c r="G152" s="11" t="s">
         <v>67</v>
       </c>
@@ -7923,12 +7891,12 @@
         <v>18</v>
       </c>
       <c r="I152" s="12">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>69</v>
@@ -7937,14 +7905,14 @@
         <v>96</v>
       </c>
       <c r="D153" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="F153" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="E153" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>549</v>
-      </c>
       <c r="G153" s="5" t="s">
         <v>67</v>
       </c>
@@ -7952,30 +7920,30 @@
         <v>18</v>
       </c>
       <c r="I153" s="8">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E154" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D154" s="10" t="s">
+      <c r="F154" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E154" s="10" t="s">
+      <c r="G154" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="F154" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G154" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="H154" s="7" t="s">
         <v>18</v>
@@ -7986,7 +7954,7 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>12</v>
@@ -8010,12 +7978,12 @@
         <v>18</v>
       </c>
       <c r="I155" s="8">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>20</v>
@@ -8039,12 +8007,12 @@
         <v>18</v>
       </c>
       <c r="I156" s="12">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>27</v>
@@ -8056,7 +8024,7 @@
         <v>29</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>31</v>
@@ -8068,12 +8036,12 @@
         <v>18</v>
       </c>
       <c r="I157" s="8">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>34</v>
@@ -8097,12 +8065,12 @@
         <v>18</v>
       </c>
       <c r="I158" s="12">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>41</v>
@@ -8126,12 +8094,12 @@
         <v>18</v>
       </c>
       <c r="I159" s="8">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B160" s="10" t="s">
         <v>48</v>
@@ -8155,12 +8123,12 @@
         <v>18</v>
       </c>
       <c r="I160" s="12">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>55</v>
@@ -8184,12 +8152,12 @@
         <v>18</v>
       </c>
       <c r="I161" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B162" s="10" t="s">
         <v>62</v>
@@ -8198,14 +8166,14 @@
         <v>63</v>
       </c>
       <c r="D162" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="F162" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="E162" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="F162" s="10" t="s">
-        <v>562</v>
-      </c>
       <c r="G162" s="11" t="s">
         <v>67</v>
       </c>
@@ -8213,12 +8181,12 @@
         <v>18</v>
       </c>
       <c r="I162" s="12">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>69</v>
@@ -8227,14 +8195,14 @@
         <v>70</v>
       </c>
       <c r="D163" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F163" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="E163" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>566</v>
-      </c>
       <c r="G163" s="5" t="s">
         <v>67</v>
       </c>
@@ -8242,12 +8210,12 @@
         <v>18</v>
       </c>
       <c r="I163" s="8">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>75</v>
@@ -8256,14 +8224,14 @@
         <v>76</v>
       </c>
       <c r="D164" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="F164" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="E164" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="F164" s="10" t="s">
-        <v>570</v>
-      </c>
       <c r="G164" s="11" t="s">
         <v>67</v>
       </c>
@@ -8271,12 +8239,12 @@
         <v>18</v>
       </c>
       <c r="I164" s="12">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>12</v>
@@ -8285,27 +8253,27 @@
         <v>81</v>
       </c>
       <c r="D165" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="F165" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="E165" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="G165" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H165" s="13" t="s">
-        <v>145</v>
+      <c r="G165" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I165" s="8">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B166" s="10" t="s">
         <v>20</v>
@@ -8314,14 +8282,14 @@
         <v>86</v>
       </c>
       <c r="D166" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="F166" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="E166" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="F166" s="10" t="s">
-        <v>578</v>
-      </c>
       <c r="G166" s="11" t="s">
         <v>67</v>
       </c>
@@ -8329,12 +8297,12 @@
         <v>18</v>
       </c>
       <c r="I166" s="12">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>27</v>
@@ -8343,14 +8311,14 @@
         <v>91</v>
       </c>
       <c r="D167" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="F167" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="E167" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>582</v>
-      </c>
       <c r="G167" s="5" t="s">
         <v>67</v>
       </c>
@@ -8358,12 +8326,12 @@
         <v>18</v>
       </c>
       <c r="I167" s="8">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B168" s="10" t="s">
         <v>34</v>
@@ -8372,14 +8340,14 @@
         <v>96</v>
       </c>
       <c r="D168" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="E168" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="F168" s="10" t="s">
         <v>584</v>
       </c>
-      <c r="E168" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="F168" s="10" t="s">
-        <v>586</v>
-      </c>
       <c r="G168" s="11" t="s">
         <v>67</v>
       </c>
@@ -8387,12 +8355,12 @@
         <v>18</v>
       </c>
       <c r="I168" s="12">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>41</v>
@@ -8401,14 +8369,14 @@
         <v>101</v>
       </c>
       <c r="D169" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="F169" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="E169" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="F169" s="6" t="s">
-        <v>590</v>
-      </c>
       <c r="G169" s="5" t="s">
         <v>67</v>
       </c>
@@ -8416,12 +8384,12 @@
         <v>18</v>
       </c>
       <c r="I169" s="8">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B170" s="10" t="s">
         <v>48</v>
@@ -8430,13 +8398,13 @@
         <v>106</v>
       </c>
       <c r="D170" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="E170" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="F170" s="10" t="s">
         <v>592</v>
-      </c>
-      <c r="E170" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="F170" s="10" t="s">
-        <v>594</v>
       </c>
       <c r="G170" s="11" t="s">
         <v>67</v>
@@ -8450,7 +8418,7 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>55</v>
@@ -8459,14 +8427,14 @@
         <v>111</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="F171" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="E171" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="F171" s="6" t="s">
-        <v>598</v>
-      </c>
       <c r="G171" s="5" t="s">
         <v>67</v>
       </c>
@@ -8474,12 +8442,12 @@
         <v>18</v>
       </c>
       <c r="I171" s="8">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>62</v>
@@ -8488,14 +8456,14 @@
         <v>116</v>
       </c>
       <c r="D172" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F172" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="E172" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="F172" s="10" t="s">
-        <v>602</v>
-      </c>
       <c r="G172" s="11" t="s">
         <v>67</v>
       </c>
@@ -8503,12 +8471,12 @@
         <v>18</v>
       </c>
       <c r="I172" s="12">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>69</v>
@@ -8517,14 +8485,14 @@
         <v>121</v>
       </c>
       <c r="D173" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F173" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="E173" s="6" t="s">
-        <v>605</v>
-      </c>
-      <c r="F173" s="6" t="s">
-        <v>606</v>
-      </c>
       <c r="G173" s="5" t="s">
         <v>67</v>
       </c>
@@ -8532,12 +8500,12 @@
         <v>18</v>
       </c>
       <c r="I173" s="8">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B174" s="10" t="s">
         <v>75</v>
@@ -8546,14 +8514,14 @@
         <v>126</v>
       </c>
       <c r="D174" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="E174" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="F174" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="E174" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="F174" s="10" t="s">
-        <v>610</v>
-      </c>
       <c r="G174" s="11" t="s">
         <v>67</v>
       </c>
@@ -8561,12 +8529,12 @@
         <v>18</v>
       </c>
       <c r="I174" s="12">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>12</v>
@@ -8575,14 +8543,14 @@
         <v>131</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F175" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="E175" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>614</v>
-      </c>
       <c r="G175" s="5" t="s">
         <v>67</v>
       </c>
@@ -8590,12 +8558,12 @@
         <v>18</v>
       </c>
       <c r="I175" s="8">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B176" s="10" t="s">
         <v>20</v>
@@ -8604,14 +8572,14 @@
         <v>136</v>
       </c>
       <c r="D176" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="F176" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="E176" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="F176" s="10" t="s">
-        <v>618</v>
-      </c>
       <c r="G176" s="11" t="s">
         <v>67</v>
       </c>
@@ -8619,12 +8587,12 @@
         <v>18</v>
       </c>
       <c r="I176" s="12">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>27</v>
@@ -8633,14 +8601,14 @@
         <v>63</v>
       </c>
       <c r="D177" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="F177" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="E177" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>622</v>
-      </c>
       <c r="G177" s="5" t="s">
         <v>67</v>
       </c>
@@ -8648,12 +8616,12 @@
         <v>18</v>
       </c>
       <c r="I177" s="8">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B178" s="10" t="s">
         <v>34</v>
@@ -8662,14 +8630,14 @@
         <v>70</v>
       </c>
       <c r="D178" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="E178" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="F178" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="E178" s="10" t="s">
-        <v>625</v>
-      </c>
-      <c r="F178" s="10" t="s">
-        <v>626</v>
-      </c>
       <c r="G178" s="11" t="s">
         <v>67</v>
       </c>
@@ -8677,41 +8645,41 @@
         <v>18</v>
       </c>
       <c r="I178" s="12">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C179" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E179" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D179" s="6" t="s">
+      <c r="F179" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E179" s="6" t="s">
+      <c r="G179" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F179" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H179" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I179" s="8">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>48</v>
@@ -8720,10 +8688,10 @@
         <v>13</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E180" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F180" s="10" t="s">
         <v>16</v>
@@ -8735,12 +8703,12 @@
         <v>18</v>
       </c>
       <c r="I180" s="12">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>55</v>
@@ -8764,12 +8732,12 @@
         <v>18</v>
       </c>
       <c r="I181" s="8">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>62</v>
@@ -8781,7 +8749,7 @@
         <v>29</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>31</v>
@@ -8793,12 +8761,12 @@
         <v>18</v>
       </c>
       <c r="I182" s="12">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>69</v>
@@ -8822,12 +8790,12 @@
         <v>18</v>
       </c>
       <c r="I183" s="8">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="9" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B184" s="10" t="s">
         <v>75</v>
@@ -8851,12 +8819,12 @@
         <v>18</v>
       </c>
       <c r="I184" s="12">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>12</v>
@@ -8880,12 +8848,12 @@
         <v>18</v>
       </c>
       <c r="I185" s="8">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="9" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B186" s="10" t="s">
         <v>20</v>
@@ -8909,12 +8877,12 @@
         <v>18</v>
       </c>
       <c r="I186" s="12">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>27</v>
@@ -8923,14 +8891,14 @@
         <v>116</v>
       </c>
       <c r="D187" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="F187" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="E187" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>639</v>
-      </c>
       <c r="G187" s="5" t="s">
         <v>67</v>
       </c>
@@ -8938,12 +8906,12 @@
         <v>18</v>
       </c>
       <c r="I187" s="8">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B188" s="10" t="s">
         <v>34</v>
@@ -8952,27 +8920,27 @@
         <v>121</v>
       </c>
       <c r="D188" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="F188" s="10" t="s">
         <v>641</v>
       </c>
-      <c r="E188" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="F188" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="G188" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H188" s="13" t="s">
-        <v>145</v>
+      <c r="G188" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H188" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I188" s="12">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>41</v>
@@ -8981,14 +8949,14 @@
         <v>126</v>
       </c>
       <c r="D189" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="F189" s="6" t="s">
         <v>645</v>
       </c>
-      <c r="E189" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="F189" s="6" t="s">
-        <v>647</v>
-      </c>
       <c r="G189" s="5" t="s">
         <v>67</v>
       </c>
@@ -8996,12 +8964,12 @@
         <v>18</v>
       </c>
       <c r="I189" s="8">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B190" s="10" t="s">
         <v>48</v>
@@ -9010,14 +8978,14 @@
         <v>131</v>
       </c>
       <c r="D190" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="E190" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="F190" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="E190" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>651</v>
-      </c>
       <c r="G190" s="11" t="s">
         <v>67</v>
       </c>
@@ -9025,12 +8993,12 @@
         <v>18</v>
       </c>
       <c r="I190" s="12">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>55</v>
@@ -9039,14 +9007,14 @@
         <v>136</v>
       </c>
       <c r="D191" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="F191" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="E191" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="F191" s="6" t="s">
-        <v>655</v>
-      </c>
       <c r="G191" s="5" t="s">
         <v>67</v>
       </c>
@@ -9054,12 +9022,12 @@
         <v>18</v>
       </c>
       <c r="I191" s="8">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B192" s="10" t="s">
         <v>62</v>
@@ -9068,14 +9036,14 @@
         <v>63</v>
       </c>
       <c r="D192" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="F192" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="E192" s="10" t="s">
-        <v>658</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>659</v>
-      </c>
       <c r="G192" s="11" t="s">
         <v>67</v>
       </c>
@@ -9083,12 +9051,12 @@
         <v>18</v>
       </c>
       <c r="I192" s="12">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>69</v>
@@ -9097,14 +9065,14 @@
         <v>70</v>
       </c>
       <c r="D193" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="F193" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="E193" s="6" t="s">
-        <v>662</v>
-      </c>
-      <c r="F193" s="6" t="s">
-        <v>663</v>
-      </c>
       <c r="G193" s="5" t="s">
         <v>67</v>
       </c>
@@ -9112,12 +9080,12 @@
         <v>18</v>
       </c>
       <c r="I193" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>75</v>
@@ -9126,14 +9094,14 @@
         <v>76</v>
       </c>
       <c r="D194" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="E194" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="F194" s="10" t="s">
         <v>665</v>
       </c>
-      <c r="E194" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>667</v>
-      </c>
       <c r="G194" s="11" t="s">
         <v>67</v>
       </c>
@@ -9141,12 +9109,12 @@
         <v>18</v>
       </c>
       <c r="I194" s="12">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>12</v>
@@ -9155,14 +9123,14 @@
         <v>81</v>
       </c>
       <c r="D195" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="F195" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="E195" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="F195" s="6" t="s">
-        <v>671</v>
-      </c>
       <c r="G195" s="5" t="s">
         <v>67</v>
       </c>
@@ -9170,12 +9138,12 @@
         <v>18</v>
       </c>
       <c r="I195" s="8">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>20</v>
@@ -9184,14 +9152,14 @@
         <v>86</v>
       </c>
       <c r="D196" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="F196" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="E196" s="10" t="s">
-        <v>674</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>675</v>
-      </c>
       <c r="G196" s="11" t="s">
         <v>67</v>
       </c>
@@ -9199,12 +9167,12 @@
         <v>18</v>
       </c>
       <c r="I196" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>27</v>
@@ -9213,14 +9181,14 @@
         <v>91</v>
       </c>
       <c r="D197" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="F197" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="E197" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="F197" s="6" t="s">
-        <v>679</v>
-      </c>
       <c r="G197" s="5" t="s">
         <v>67</v>
       </c>
@@ -9228,12 +9196,12 @@
         <v>18</v>
       </c>
       <c r="I197" s="8">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B198" s="10" t="s">
         <v>34</v>
@@ -9242,14 +9210,14 @@
         <v>96</v>
       </c>
       <c r="D198" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="F198" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="E198" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>683</v>
-      </c>
       <c r="G198" s="11" t="s">
         <v>67</v>
       </c>
@@ -9257,12 +9225,12 @@
         <v>18</v>
       </c>
       <c r="I198" s="12">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>41</v>
@@ -9271,14 +9239,14 @@
         <v>101</v>
       </c>
       <c r="D199" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F199" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="E199" s="6" t="s">
-        <v>686</v>
-      </c>
-      <c r="F199" s="6" t="s">
-        <v>687</v>
-      </c>
       <c r="G199" s="5" t="s">
         <v>67</v>
       </c>
@@ -9286,12 +9254,12 @@
         <v>18</v>
       </c>
       <c r="I199" s="8">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="9" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B200" s="10" t="s">
         <v>48</v>
@@ -9300,14 +9268,14 @@
         <v>106</v>
       </c>
       <c r="D200" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="F200" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="E200" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>691</v>
-      </c>
       <c r="G200" s="11" t="s">
         <v>67</v>
       </c>
@@ -9315,12 +9283,12 @@
         <v>18</v>
       </c>
       <c r="I200" s="12">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>55</v>
@@ -9329,14 +9297,14 @@
         <v>111</v>
       </c>
       <c r="D201" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="F201" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="E201" s="6" t="s">
-        <v>694</v>
-      </c>
-      <c r="F201" s="6" t="s">
-        <v>695</v>
-      </c>
       <c r="G201" s="5" t="s">
         <v>67</v>
       </c>
@@ -9344,12 +9312,12 @@
         <v>18</v>
       </c>
       <c r="I201" s="8">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="9" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>62</v>
@@ -9358,14 +9326,14 @@
         <v>116</v>
       </c>
       <c r="D202" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="E202" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="F202" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="E202" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="F202" s="10" t="s">
-        <v>699</v>
-      </c>
       <c r="G202" s="11" t="s">
         <v>67</v>
       </c>
@@ -9373,12 +9341,12 @@
         <v>18</v>
       </c>
       <c r="I202" s="12">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>69</v>
@@ -9387,14 +9355,14 @@
         <v>121</v>
       </c>
       <c r="D203" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="F203" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="E203" s="6" t="s">
-        <v>702</v>
-      </c>
-      <c r="F203" s="6" t="s">
-        <v>703</v>
-      </c>
       <c r="G203" s="5" t="s">
         <v>67</v>
       </c>
@@ -9402,41 +9370,41 @@
         <v>18</v>
       </c>
       <c r="I203" s="8">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="9" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B204" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C204" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D204" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E204" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="F204" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E204" s="10" t="s">
+      <c r="G204" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F204" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G204" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="H204" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I204" s="12">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>12</v>
@@ -9445,10 +9413,10 @@
         <v>13</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F205" s="6" t="s">
         <v>16</v>
@@ -9460,12 +9428,12 @@
         <v>18</v>
       </c>
       <c r="I205" s="8">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>20</v>
@@ -9489,12 +9457,12 @@
         <v>18</v>
       </c>
       <c r="I206" s="12">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>27</v>
@@ -9506,7 +9474,7 @@
         <v>29</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>31</v>
@@ -9518,12 +9486,12 @@
         <v>18</v>
       </c>
       <c r="I207" s="8">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>34</v>
@@ -9547,12 +9515,12 @@
         <v>18</v>
       </c>
       <c r="I208" s="12">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>41</v>
@@ -9576,12 +9544,12 @@
         <v>18</v>
       </c>
       <c r="I209" s="8">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>48</v>
@@ -9605,12 +9573,12 @@
         <v>18</v>
       </c>
       <c r="I210" s="12">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>55</v>
@@ -9628,18 +9596,18 @@
         <v>59</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="H211" s="13" t="s">
-        <v>145</v>
+        <v>60</v>
+      </c>
+      <c r="H211" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I211" s="8">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>62</v>
@@ -9648,13 +9616,13 @@
         <v>91</v>
       </c>
       <c r="D212" s="10" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G212" s="11" t="s">
         <v>67</v>
@@ -9663,12 +9631,12 @@
         <v>18</v>
       </c>
       <c r="I212" s="12">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>69</v>
@@ -9677,13 +9645,13 @@
         <v>96</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="G213" s="5" t="s">
         <v>67</v>
@@ -9692,12 +9660,12 @@
         <v>18</v>
       </c>
       <c r="I213" s="8">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="9" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>75</v>
@@ -9706,13 +9674,13 @@
         <v>101</v>
       </c>
       <c r="D214" s="10" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G214" s="11" t="s">
         <v>67</v>
@@ -9721,12 +9689,12 @@
         <v>18</v>
       </c>
       <c r="I214" s="12">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>12</v>
@@ -9735,13 +9703,13 @@
         <v>106</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="G215" s="5" t="s">
         <v>67</v>
@@ -9750,12 +9718,12 @@
         <v>18</v>
       </c>
       <c r="I215" s="8">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="9" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B216" s="10" t="s">
         <v>20</v>
@@ -9764,13 +9732,13 @@
         <v>111</v>
       </c>
       <c r="D216" s="10" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E216" s="10" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="G216" s="11" t="s">
         <v>67</v>
@@ -9779,12 +9747,12 @@
         <v>18</v>
       </c>
       <c r="I216" s="12">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>27</v>
@@ -9793,13 +9761,13 @@
         <v>116</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G217" s="5" t="s">
         <v>67</v>
@@ -9808,12 +9776,12 @@
         <v>18</v>
       </c>
       <c r="I217" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="9" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B218" s="10" t="s">
         <v>34</v>
@@ -9822,13 +9790,13 @@
         <v>121</v>
       </c>
       <c r="D218" s="10" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E218" s="10" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G218" s="11" t="s">
         <v>67</v>
@@ -9837,12 +9805,12 @@
         <v>18</v>
       </c>
       <c r="I218" s="12">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>41</v>
@@ -9851,13 +9819,13 @@
         <v>126</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>67</v>
@@ -9866,12 +9834,12 @@
         <v>18</v>
       </c>
       <c r="I219" s="8">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="9" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B220" s="10" t="s">
         <v>48</v>
@@ -9880,13 +9848,13 @@
         <v>131</v>
       </c>
       <c r="D220" s="10" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="G220" s="11" t="s">
         <v>67</v>
@@ -9895,12 +9863,12 @@
         <v>18</v>
       </c>
       <c r="I220" s="12">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>55</v>
@@ -9909,13 +9877,13 @@
         <v>136</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G221" s="5" t="s">
         <v>67</v>
@@ -9924,12 +9892,12 @@
         <v>18</v>
       </c>
       <c r="I221" s="8">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>62</v>
@@ -9938,13 +9906,13 @@
         <v>63</v>
       </c>
       <c r="D222" s="10" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E222" s="10" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G222" s="11" t="s">
         <v>67</v>
@@ -9953,12 +9921,12 @@
         <v>18</v>
       </c>
       <c r="I222" s="12">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>69</v>
@@ -9967,13 +9935,13 @@
         <v>70</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>67</v>
@@ -9982,12 +9950,12 @@
         <v>18</v>
       </c>
       <c r="I223" s="8">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>75</v>
@@ -9996,13 +9964,13 @@
         <v>76</v>
       </c>
       <c r="D224" s="10" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E224" s="10" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="G224" s="11" t="s">
         <v>67</v>
@@ -10011,12 +9979,12 @@
         <v>18</v>
       </c>
       <c r="I224" s="12">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>12</v>
@@ -10025,13 +9993,13 @@
         <v>81</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>67</v>
@@ -10040,12 +10008,12 @@
         <v>18</v>
       </c>
       <c r="I225" s="8">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>20</v>
@@ -10054,13 +10022,13 @@
         <v>86</v>
       </c>
       <c r="D226" s="10" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="G226" s="11" t="s">
         <v>67</v>
@@ -10069,12 +10037,12 @@
         <v>18</v>
       </c>
       <c r="I226" s="12">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>27</v>
@@ -10083,13 +10051,13 @@
         <v>91</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>67</v>
@@ -10098,12 +10066,12 @@
         <v>18</v>
       </c>
       <c r="I227" s="8">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>34</v>
@@ -10112,13 +10080,13 @@
         <v>96</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E228" s="10" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="G228" s="11" t="s">
         <v>67</v>
@@ -10127,41 +10095,41 @@
         <v>18</v>
       </c>
       <c r="I228" s="12">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C229" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E229" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D229" s="6" t="s">
+      <c r="F229" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E229" s="6" t="s">
+      <c r="G229" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F229" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G229" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H229" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I229" s="8">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>48</v>
@@ -10170,10 +10138,10 @@
         <v>13</v>
       </c>
       <c r="D230" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E230" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F230" s="10" t="s">
         <v>16</v>
@@ -10185,12 +10153,12 @@
         <v>18</v>
       </c>
       <c r="I230" s="12">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>55</v>
@@ -10214,12 +10182,12 @@
         <v>18</v>
       </c>
       <c r="I231" s="8">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B232" s="10" t="s">
         <v>62</v>
@@ -10231,7 +10199,7 @@
         <v>29</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="F232" s="10" t="s">
         <v>31</v>
@@ -10243,12 +10211,12 @@
         <v>18</v>
       </c>
       <c r="I232" s="12">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>69</v>
@@ -10272,12 +10240,12 @@
         <v>18</v>
       </c>
       <c r="I233" s="8">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B234" s="10" t="s">
         <v>75</v>
@@ -10294,19 +10262,19 @@
       <c r="F234" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G234" s="10" t="s">
-        <v>789</v>
-      </c>
-      <c r="H234" s="13" t="s">
-        <v>145</v>
+      <c r="G234" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H234" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I234" s="12">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>12</v>
@@ -10330,12 +10298,12 @@
         <v>18</v>
       </c>
       <c r="I235" s="8">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B236" s="10" t="s">
         <v>20</v>
@@ -10359,12 +10327,12 @@
         <v>18</v>
       </c>
       <c r="I236" s="12">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>27</v>
@@ -10373,13 +10341,13 @@
         <v>63</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="G237" s="5" t="s">
         <v>67</v>
@@ -10393,7 +10361,7 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>34</v>
@@ -10402,13 +10370,13 @@
         <v>70</v>
       </c>
       <c r="D238" s="10" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="E238" s="10" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="F238" s="10" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G238" s="11" t="s">
         <v>67</v>
@@ -10417,12 +10385,12 @@
         <v>18</v>
       </c>
       <c r="I238" s="12">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>41</v>
@@ -10431,13 +10399,13 @@
         <v>76</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="G239" s="5" t="s">
         <v>67</v>
@@ -10446,12 +10414,12 @@
         <v>18</v>
       </c>
       <c r="I239" s="8">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B240" s="10" t="s">
         <v>48</v>
@@ -10460,13 +10428,13 @@
         <v>81</v>
       </c>
       <c r="D240" s="10" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E240" s="10" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F240" s="10" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="G240" s="11" t="s">
         <v>67</v>
@@ -10475,12 +10443,12 @@
         <v>18</v>
       </c>
       <c r="I240" s="12">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>55</v>
@@ -10489,13 +10457,13 @@
         <v>86</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="G241" s="5" t="s">
         <v>67</v>
@@ -10509,7 +10477,7 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B242" s="10" t="s">
         <v>62</v>
@@ -10518,13 +10486,13 @@
         <v>91</v>
       </c>
       <c r="D242" s="10" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="E242" s="10" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="F242" s="10" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="G242" s="11" t="s">
         <v>67</v>
@@ -10533,12 +10501,12 @@
         <v>18</v>
       </c>
       <c r="I242" s="12">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>69</v>
@@ -10547,13 +10515,13 @@
         <v>96</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>67</v>
@@ -10562,12 +10530,12 @@
         <v>18</v>
       </c>
       <c r="I243" s="8">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>75</v>
@@ -10576,13 +10544,13 @@
         <v>101</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E244" s="10" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="G244" s="11" t="s">
         <v>67</v>
@@ -10591,12 +10559,12 @@
         <v>18</v>
       </c>
       <c r="I244" s="12">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>12</v>
@@ -10605,13 +10573,13 @@
         <v>106</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="F245" s="6" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="G245" s="5" t="s">
         <v>67</v>
@@ -10620,12 +10588,12 @@
         <v>18</v>
       </c>
       <c r="I245" s="8">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="9" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>20</v>
@@ -10634,13 +10602,13 @@
         <v>111</v>
       </c>
       <c r="D246" s="10" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="F246" s="10" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G246" s="11" t="s">
         <v>67</v>
@@ -10649,12 +10617,12 @@
         <v>18</v>
       </c>
       <c r="I246" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>27</v>
@@ -10663,13 +10631,13 @@
         <v>116</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>67</v>
@@ -10678,12 +10646,12 @@
         <v>18</v>
       </c>
       <c r="I247" s="8">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="9" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B248" s="10" t="s">
         <v>34</v>
@@ -10692,13 +10660,13 @@
         <v>121</v>
       </c>
       <c r="D248" s="10" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="F248" s="10" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G248" s="11" t="s">
         <v>67</v>
@@ -10707,12 +10675,12 @@
         <v>18</v>
       </c>
       <c r="I248" s="12">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>41</v>
@@ -10721,13 +10689,13 @@
         <v>126</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="G249" s="5" t="s">
         <v>67</v>
@@ -10736,12 +10704,12 @@
         <v>18</v>
       </c>
       <c r="I249" s="8">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="9" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B250" s="10" t="s">
         <v>48</v>
@@ -10750,13 +10718,13 @@
         <v>131</v>
       </c>
       <c r="D250" s="10" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="F250" s="10" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="G250" s="11" t="s">
         <v>67</v>
@@ -10765,12 +10733,12 @@
         <v>18</v>
       </c>
       <c r="I250" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>55</v>
@@ -10779,13 +10747,13 @@
         <v>136</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="G251" s="5" t="s">
         <v>67</v>
@@ -10794,12 +10762,12 @@
         <v>18</v>
       </c>
       <c r="I251" s="8">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B252" s="10" t="s">
         <v>62</v>
@@ -10808,13 +10776,13 @@
         <v>63</v>
       </c>
       <c r="D252" s="10" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F252" s="10" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G252" s="11" t="s">
         <v>67</v>
@@ -10823,12 +10791,12 @@
         <v>18</v>
       </c>
       <c r="I252" s="12">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>69</v>
@@ -10837,13 +10805,13 @@
         <v>70</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>67</v>
@@ -10852,41 +10820,41 @@
         <v>18</v>
       </c>
       <c r="I253" s="8">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="9" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C254" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E254" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D254" s="10" t="s">
+      <c r="F254" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E254" s="10" t="s">
+      <c r="G254" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F254" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G254" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="H254" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I254" s="12">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>12</v>
@@ -10895,10 +10863,10 @@
         <v>13</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F255" s="6" t="s">
         <v>16</v>
@@ -10910,12 +10878,12 @@
         <v>18</v>
       </c>
       <c r="I255" s="8">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="9" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B256" s="10" t="s">
         <v>20</v>
@@ -10939,12 +10907,12 @@
         <v>18</v>
       </c>
       <c r="I256" s="12">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>27</v>
@@ -10956,24 +10924,24 @@
         <v>29</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F257" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G257" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="H257" s="13" t="s">
-        <v>145</v>
+      <c r="G257" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H257" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I257" s="8">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="9" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>34</v>
@@ -10997,12 +10965,12 @@
         <v>18</v>
       </c>
       <c r="I258" s="12">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>41</v>
@@ -11026,12 +10994,12 @@
         <v>18</v>
       </c>
       <c r="I259" s="8">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="9" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>48</v>
@@ -11055,12 +11023,12 @@
         <v>18</v>
       </c>
       <c r="I260" s="12">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>55</v>
@@ -11084,12 +11052,12 @@
         <v>18</v>
       </c>
       <c r="I261" s="8">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="9" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>62</v>
@@ -11098,13 +11066,13 @@
         <v>116</v>
       </c>
       <c r="D262" s="10" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="E262" s="10" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="F262" s="10" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G262" s="11" t="s">
         <v>67</v>
@@ -11113,12 +11081,12 @@
         <v>18</v>
       </c>
       <c r="I262" s="12">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>69</v>
@@ -11127,13 +11095,13 @@
         <v>121</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="E263" s="6" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="F263" s="6" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G263" s="5" t="s">
         <v>67</v>
@@ -11142,12 +11110,12 @@
         <v>18</v>
       </c>
       <c r="I263" s="8">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="9" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>75</v>
@@ -11156,13 +11124,13 @@
         <v>126</v>
       </c>
       <c r="D264" s="10" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="E264" s="10" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="F264" s="10" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G264" s="11" t="s">
         <v>67</v>
@@ -11171,12 +11139,12 @@
         <v>18</v>
       </c>
       <c r="I264" s="12">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>12</v>
@@ -11185,13 +11153,13 @@
         <v>131</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="G265" s="5" t="s">
         <v>67</v>
@@ -11200,12 +11168,12 @@
         <v>18</v>
       </c>
       <c r="I265" s="8">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="9" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>20</v>
@@ -11214,13 +11182,13 @@
         <v>136</v>
       </c>
       <c r="D266" s="10" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="E266" s="10" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="F266" s="10" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="G266" s="11" t="s">
         <v>67</v>
@@ -11229,12 +11197,12 @@
         <v>18</v>
       </c>
       <c r="I266" s="12">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>27</v>
@@ -11243,13 +11211,13 @@
         <v>63</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="G267" s="5" t="s">
         <v>67</v>
@@ -11258,12 +11226,12 @@
         <v>18</v>
       </c>
       <c r="I267" s="8">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="9" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>34</v>
@@ -11272,13 +11240,13 @@
         <v>70</v>
       </c>
       <c r="D268" s="10" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E268" s="10" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="F268" s="10" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="G268" s="11" t="s">
         <v>67</v>
@@ -11287,12 +11255,12 @@
         <v>18</v>
       </c>
       <c r="I268" s="12">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>41</v>
@@ -11301,13 +11269,13 @@
         <v>76</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="F269" s="6" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="G269" s="5" t="s">
         <v>67</v>
@@ -11316,12 +11284,12 @@
         <v>18</v>
       </c>
       <c r="I269" s="8">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="9" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>48</v>
@@ -11330,13 +11298,13 @@
         <v>81</v>
       </c>
       <c r="D270" s="10" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="E270" s="10" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="F270" s="10" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="G270" s="11" t="s">
         <v>67</v>
@@ -11345,12 +11313,12 @@
         <v>18</v>
       </c>
       <c r="I270" s="12">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>55</v>
@@ -11359,13 +11327,13 @@
         <v>86</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="F271" s="6" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="G271" s="5" t="s">
         <v>67</v>
@@ -11374,12 +11342,12 @@
         <v>18</v>
       </c>
       <c r="I271" s="8">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="9" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>62</v>
@@ -11388,13 +11356,13 @@
         <v>91</v>
       </c>
       <c r="D272" s="10" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="E272" s="10" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F272" s="10" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="G272" s="11" t="s">
         <v>67</v>
@@ -11403,12 +11371,12 @@
         <v>18</v>
       </c>
       <c r="I272" s="12">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>69</v>
@@ -11417,13 +11385,13 @@
         <v>96</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="G273" s="5" t="s">
         <v>67</v>
@@ -11432,12 +11400,12 @@
         <v>18</v>
       </c>
       <c r="I273" s="8">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="9" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>75</v>
@@ -11446,13 +11414,13 @@
         <v>101</v>
       </c>
       <c r="D274" s="10" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="E274" s="10" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="F274" s="10" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="G274" s="11" t="s">
         <v>67</v>
@@ -11461,12 +11429,12 @@
         <v>18</v>
       </c>
       <c r="I274" s="12">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>12</v>
@@ -11475,13 +11443,13 @@
         <v>106</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="F275" s="6" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G275" s="5" t="s">
         <v>67</v>
@@ -11490,12 +11458,12 @@
         <v>18</v>
       </c>
       <c r="I275" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="9" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>20</v>
@@ -11504,13 +11472,13 @@
         <v>111</v>
       </c>
       <c r="D276" s="10" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="E276" s="10" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="F276" s="10" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="G276" s="11" t="s">
         <v>67</v>
@@ -11519,12 +11487,12 @@
         <v>18</v>
       </c>
       <c r="I276" s="12">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>27</v>
@@ -11533,13 +11501,13 @@
         <v>116</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="F277" s="6" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>67</v>
@@ -11548,12 +11516,12 @@
         <v>18</v>
       </c>
       <c r="I277" s="8">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="9" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>34</v>
@@ -11562,13 +11530,13 @@
         <v>121</v>
       </c>
       <c r="D278" s="10" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="E278" s="10" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="F278" s="10" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="G278" s="11" t="s">
         <v>67</v>
@@ -11577,41 +11545,41 @@
         <v>18</v>
       </c>
       <c r="I278" s="12">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C279" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E279" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D279" s="6" t="s">
+      <c r="F279" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E279" s="6" t="s">
+      <c r="G279" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F279" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G279" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H279" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I279" s="8">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="9" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>48</v>
@@ -11620,27 +11588,27 @@
         <v>13</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E280" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F280" s="10" t="s">
         <v>16</v>
       </c>
       <c r="G280" s="10" t="s">
-        <v>940</v>
-      </c>
-      <c r="H280" s="13" t="s">
-        <v>145</v>
+        <v>17</v>
+      </c>
+      <c r="H280" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I280" s="12">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>55</v>
@@ -11664,12 +11632,12 @@
         <v>18</v>
       </c>
       <c r="I281" s="8">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="9" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>62</v>
@@ -11681,7 +11649,7 @@
         <v>29</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="F282" s="10" t="s">
         <v>31</v>
@@ -11693,12 +11661,12 @@
         <v>18</v>
       </c>
       <c r="I282" s="12">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>69</v>
@@ -11722,12 +11690,12 @@
         <v>18</v>
       </c>
       <c r="I283" s="8">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="9" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>75</v>
@@ -11751,12 +11719,12 @@
         <v>18</v>
       </c>
       <c r="I284" s="12">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>12</v>
@@ -11780,12 +11748,12 @@
         <v>18</v>
       </c>
       <c r="I285" s="8">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="9" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>20</v>
@@ -11809,12 +11777,12 @@
         <v>18</v>
       </c>
       <c r="I286" s="12">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>27</v>
@@ -11823,13 +11791,13 @@
         <v>91</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="E287" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="F287" s="6" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="G287" s="5" t="s">
         <v>67</v>
@@ -11838,12 +11806,12 @@
         <v>18</v>
       </c>
       <c r="I287" s="8">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="9" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>34</v>
@@ -11852,13 +11820,13 @@
         <v>96</v>
       </c>
       <c r="D288" s="10" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="E288" s="10" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="F288" s="10" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="G288" s="11" t="s">
         <v>67</v>
@@ -11867,12 +11835,12 @@
         <v>18</v>
       </c>
       <c r="I288" s="12">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>41</v>
@@ -11881,13 +11849,13 @@
         <v>101</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="E289" s="6" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="F289" s="6" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="G289" s="5" t="s">
         <v>67</v>
@@ -11896,12 +11864,12 @@
         <v>18</v>
       </c>
       <c r="I289" s="8">
-        <v>11</v>
+        <v>49</v>
       </c>
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="9" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>48</v>
@@ -11910,13 +11878,13 @@
         <v>106</v>
       </c>
       <c r="D290" s="10" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="E290" s="10" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="F290" s="10" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="G290" s="11" t="s">
         <v>67</v>
@@ -11925,12 +11893,12 @@
         <v>18</v>
       </c>
       <c r="I290" s="12">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>55</v>
@@ -11939,13 +11907,13 @@
         <v>111</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="F291" s="6" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="G291" s="5" t="s">
         <v>67</v>
@@ -11954,12 +11922,12 @@
         <v>18</v>
       </c>
       <c r="I291" s="8">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="9" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>62</v>
@@ -11968,13 +11936,13 @@
         <v>116</v>
       </c>
       <c r="D292" s="10" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="E292" s="10" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="F292" s="10" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="G292" s="11" t="s">
         <v>67</v>
@@ -11983,12 +11951,12 @@
         <v>18</v>
       </c>
       <c r="I292" s="12">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>69</v>
@@ -11997,13 +11965,13 @@
         <v>121</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="E293" s="6" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F293" s="6" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="G293" s="5" t="s">
         <v>67</v>
@@ -12012,12 +11980,12 @@
         <v>18</v>
       </c>
       <c r="I293" s="8">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="9" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>75</v>
@@ -12026,13 +11994,13 @@
         <v>126</v>
       </c>
       <c r="D294" s="10" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="E294" s="10" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="F294" s="10" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="G294" s="11" t="s">
         <v>67</v>
@@ -12041,12 +12009,12 @@
         <v>18</v>
       </c>
       <c r="I294" s="12">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>12</v>
@@ -12055,13 +12023,13 @@
         <v>131</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="E295" s="6" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="F295" s="6" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="G295" s="5" t="s">
         <v>67</v>
@@ -12070,12 +12038,12 @@
         <v>18</v>
       </c>
       <c r="I295" s="8">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="9" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>20</v>
@@ -12084,13 +12052,13 @@
         <v>136</v>
       </c>
       <c r="D296" s="10" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="E296" s="10" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="F296" s="10" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="G296" s="11" t="s">
         <v>67</v>
@@ -12099,12 +12067,12 @@
         <v>18</v>
       </c>
       <c r="I296" s="12">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>27</v>
@@ -12113,13 +12081,13 @@
         <v>63</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="E297" s="6" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="F297" s="6" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="G297" s="5" t="s">
         <v>67</v>
@@ -12128,12 +12096,12 @@
         <v>18</v>
       </c>
       <c r="I297" s="8">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="9" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>34</v>
@@ -12142,13 +12110,13 @@
         <v>70</v>
       </c>
       <c r="D298" s="10" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="E298" s="10" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="F298" s="10" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="G298" s="11" t="s">
         <v>67</v>
@@ -12157,12 +12125,12 @@
         <v>18</v>
       </c>
       <c r="I298" s="12">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>41</v>
@@ -12171,13 +12139,13 @@
         <v>76</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="E299" s="6" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="F299" s="6" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="G299" s="5" t="s">
         <v>67</v>
@@ -12186,12 +12154,12 @@
         <v>18</v>
       </c>
       <c r="I299" s="8">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="9" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>48</v>
@@ -12200,13 +12168,13 @@
         <v>81</v>
       </c>
       <c r="D300" s="10" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="E300" s="10" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="F300" s="10" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="G300" s="11" t="s">
         <v>67</v>
@@ -12215,12 +12183,12 @@
         <v>18</v>
       </c>
       <c r="I300" s="12">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>55</v>
@@ -12229,13 +12197,13 @@
         <v>86</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="E301" s="6" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="F301" s="6" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="G301" s="5" t="s">
         <v>67</v>
@@ -12244,12 +12212,12 @@
         <v>18</v>
       </c>
       <c r="I301" s="8">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="302" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="9" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>62</v>
@@ -12258,13 +12226,13 @@
         <v>91</v>
       </c>
       <c r="D302" s="10" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="E302" s="10" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="F302" s="10" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="G302" s="11" t="s">
         <v>67</v>
@@ -12273,12 +12241,12 @@
         <v>18</v>
       </c>
       <c r="I302" s="12">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="303" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>69</v>
@@ -12287,51 +12255,51 @@
         <v>96</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="E303" s="6" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="F303" s="6" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G303" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H303" s="13" t="s">
-        <v>145</v>
+        <v>1009</v>
+      </c>
+      <c r="G303" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I303" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="304" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="9" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C304" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E304" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D304" s="10" t="s">
+      <c r="F304" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E304" s="10" t="s">
+      <c r="G304" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F304" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G304" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="H304" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I304" s="12">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
